--- a/docs/downloads/governance-maturity-dashboard.xlsx
+++ b/docs/downloads/governance-maturity-dashboard.xlsx
@@ -569,7 +569,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>FSI Agent Governance Framework v1.2.41 — February 2026</t>
+          <t>FSI Agent Governance Framework v1.3.0 — March 2026</t>
         </is>
       </c>
     </row>
@@ -608,7 +608,7 @@
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C6" s="5" t="n">
         <v>0</v>
@@ -627,7 +627,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C7" s="5" t="n">
         <v>0</v>
@@ -646,7 +646,7 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>0</v>
@@ -665,7 +665,7 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C9" s="5" t="n">
         <v>0</v>
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="C10" s="7" t="n">
         <v>0</v>
@@ -706,7 +706,7 @@
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>FSI Agent Governance Framework v1.2.41 — February 2026</t>
+          <t>FSI Agent Governance Framework v1.3.0 — March 2026</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;CGovernance Maturity Dashboard — Summary</oddHeader>
-    <oddFooter>&amp;CFSI Agent Governance Framework v1.2.41 — February 2026</oddFooter>
+    <oddFooter>&amp;CFSI Agent Governance Framework v1.3.0 — March 2026</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -736,7 +736,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -756,7 +756,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Pillar 1 — Security  |  28 Controls</t>
+          <t>Pillar 1 — Security  |  29 Controls</t>
         </is>
       </c>
     </row>
@@ -1320,10 +1320,29 @@
       <c r="D32" s="16" t="n"/>
       <c r="E32" s="18" t="n"/>
     </row>
-    <row r="34">
-      <c r="A34" s="9" t="inlineStr">
-        <is>
-          <t>FSI Agent Governance Framework v1.2.41 — February 2026</t>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="inlineStr">
+        <is>
+          <t>Global Secure Access: Network Controls for Copilot Studio Agents</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="D33" s="12" t="n"/>
+      <c r="E33" s="14" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>FSI Agent Governance Framework v1.3.0 — March 2026</t>
         </is>
       </c>
     </row>
@@ -1331,11 +1350,11 @@
   <autoFilter ref="A4:E4"/>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A34:E34"/>
     <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A35:E35"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="C5:C32" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Status" error="Please select: Not Started, In Progress, Completed, or N/A" promptTitle="Status" prompt="Select implementation status" type="list">
+    <dataValidation sqref="C5:C33" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Status" error="Please select: Not Started, In Progress, Completed, or N/A" promptTitle="Status" prompt="Select implementation status" type="list">
       <formula1>"Not Started,In Progress,Completed,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1343,7 +1362,7 @@
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;CGovernance Maturity Dashboard — Pillar 1 — Security</oddHeader>
-    <oddFooter>&amp;CFSI Agent Governance Framework v1.2.41 — February 2026</oddFooter>
+    <oddFooter>&amp;CFSI Agent Governance Framework v1.3.0 — March 2026</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1358,7 +1377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E30"/>
+  <dimension ref="A1:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1378,7 +1397,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Pillar 2 — Management  |  24 Controls</t>
+          <t>Pillar 2 — Management  |  26 Controls</t>
         </is>
       </c>
     </row>
@@ -1866,10 +1885,48 @@
       <c r="D28" s="16" t="n"/>
       <c r="E28" s="18" t="n"/>
     </row>
-    <row r="30">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>FSI Agent Governance Framework v1.2.41 — February 2026</t>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="inlineStr">
+        <is>
+          <t>Microsoft Agent 365: Admin Center Governance Console</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="n"/>
+      <c r="E29" s="14" t="n"/>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>2.26</t>
+        </is>
+      </c>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>Entra Agent ID: Identity Governance for Agents</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="D30" s="16" t="n"/>
+      <c r="E30" s="18" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
+        <is>
+          <t>FSI Agent Governance Framework v1.3.0 — March 2026</t>
         </is>
       </c>
     </row>
@@ -1878,10 +1935,10 @@
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A32:E32"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="C5:C28" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Status" error="Please select: Not Started, In Progress, Completed, or N/A" promptTitle="Status" prompt="Select implementation status" type="list">
+    <dataValidation sqref="C5:C30" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Status" error="Please select: Not Started, In Progress, Completed, or N/A" promptTitle="Status" prompt="Select implementation status" type="list">
       <formula1>"Not Started,In Progress,Completed,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1889,7 +1946,7 @@
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;CGovernance Maturity Dashboard — Pillar 2 — Management</oddHeader>
-    <oddFooter>&amp;CFSI Agent Governance Framework v1.2.41 — February 2026</oddFooter>
+    <oddFooter>&amp;CFSI Agent Governance Framework v1.3.0 — March 2026</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1904,7 +1961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1924,7 +1981,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Pillar 3 — Reporting  |  12 Controls</t>
+          <t>Pillar 3 — Reporting  |  14 Controls</t>
         </is>
       </c>
     </row>
@@ -2184,10 +2241,48 @@
       <c r="D16" s="16" t="n"/>
       <c r="E16" s="18" t="n"/>
     </row>
-    <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>FSI Agent Governance Framework v1.2.41 — February 2026</t>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>3.13</t>
+        </is>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>Agent 365 Admin Center Analytics and Reporting</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="n"/>
+      <c r="E17" s="14" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="15" t="inlineStr">
+        <is>
+          <t>3.14</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>Agent 365 Observability SDK and Custom Agent Telemetry</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="D18" s="16" t="n"/>
+      <c r="E18" s="18" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>FSI Agent Governance Framework v1.3.0 — March 2026</t>
         </is>
       </c>
     </row>
@@ -2196,10 +2291,10 @@
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="A20:E20"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="C5:C16" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Status" error="Please select: Not Started, In Progress, Completed, or N/A" promptTitle="Status" prompt="Select implementation status" type="list">
+    <dataValidation sqref="C5:C18" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Status" error="Please select: Not Started, In Progress, Completed, or N/A" promptTitle="Status" prompt="Select implementation status" type="list">
       <formula1>"Not Started,In Progress,Completed,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2207,7 +2302,7 @@
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;CGovernance Maturity Dashboard — Pillar 3 — Reporting</oddHeader>
-    <oddFooter>&amp;CFSI Agent Governance Framework v1.2.41 — February 2026</oddFooter>
+    <oddFooter>&amp;CFSI Agent Governance Framework v1.3.0 — March 2026</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2222,7 +2317,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2242,7 +2337,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Pillar 4 — SharePoint  |  7 Controls</t>
+          <t>Pillar 4 — SharePoint  |  9 Controls</t>
         </is>
       </c>
     </row>
@@ -2407,10 +2502,48 @@
       <c r="D11" s="12" t="n"/>
       <c r="E11" s="14" t="n"/>
     </row>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>FSI Agent Governance Framework v1.2.41 — February 2026</t>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>Item-Level Permission Scanning for Agent Knowledge Sources</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="n"/>
+      <c r="E12" s="18" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>Embedded File Content Governance</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>Not Started</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="n"/>
+      <c r="E13" s="14" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>FSI Agent Governance Framework v1.3.0 — March 2026</t>
         </is>
       </c>
     </row>
@@ -2418,11 +2551,11 @@
   <autoFilter ref="A4:E4"/>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A15:E15"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A13:E13"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="C5:C11" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Status" error="Please select: Not Started, In Progress, Completed, or N/A" promptTitle="Status" prompt="Select implementation status" type="list">
+    <dataValidation sqref="C5:C13" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Invalid Status" error="Please select: Not Started, In Progress, Completed, or N/A" promptTitle="Status" prompt="Select implementation status" type="list">
       <formula1>"Not Started,In Progress,Completed,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2430,7 +2563,7 @@
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;CGovernance Maturity Dashboard — Pillar 4 — SharePoint</oddHeader>
-    <oddFooter>&amp;CFSI Agent Governance Framework v1.2.41 — February 2026</oddFooter>
+    <oddFooter>&amp;CFSI Agent Governance Framework v1.3.0 — March 2026</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/docs/downloads/governance-maturity-dashboard.xlsx
+++ b/docs/downloads/governance-maturity-dashboard.xlsx
@@ -569,10 +569,11 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>FSI Agent Governance Framework v1.3.0 — March 2026</t>
-        </is>
-      </c>
-    </row>
+          <t>FSI Agent Governance Framework v1.4.0 — April 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="6" customHeight="1"/>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -696,6 +697,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
@@ -703,10 +705,11 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>FSI Agent Governance Framework v1.3.0 — March 2026</t>
+          <t>FSI Agent Governance Framework v1.4.0 — April 2026</t>
         </is>
       </c>
     </row>
@@ -1339,10 +1342,11 @@
       <c r="D33" s="12" t="n"/>
       <c r="E33" s="14" t="n"/>
     </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" s="9" t="inlineStr">
         <is>
-          <t>FSI Agent Governance Framework v1.3.0 — March 2026</t>
+          <t>FSI Agent Governance Framework v1.4.0 — April 2026</t>
         </is>
       </c>
     </row>
@@ -1923,10 +1927,11 @@
       <c r="D30" s="16" t="n"/>
       <c r="E30" s="18" t="n"/>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="9" t="inlineStr">
         <is>
-          <t>FSI Agent Governance Framework v1.3.0 — March 2026</t>
+          <t>FSI Agent Governance Framework v1.4.0 — April 2026</t>
         </is>
       </c>
     </row>
@@ -2279,10 +2284,11 @@
       <c r="D18" s="16" t="n"/>
       <c r="E18" s="18" t="n"/>
     </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>FSI Agent Governance Framework v1.3.0 — March 2026</t>
+          <t>FSI Agent Governance Framework v1.4.0 — April 2026</t>
         </is>
       </c>
     </row>
@@ -2540,10 +2546,11 @@
       <c r="D13" s="12" t="n"/>
       <c r="E13" s="14" t="n"/>
     </row>
+    <row r="14"/>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>FSI Agent Governance Framework v1.3.0 — March 2026</t>
+          <t>FSI Agent Governance Framework v1.4.0 — April 2026</t>
         </is>
       </c>
     </row>
